--- a/src/data/content/portfolio-master.xlsx
+++ b/src/data/content/portfolio-master.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="719">
   <si>
     <t>Portfolio Content Hub</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Edit the workbook from a single control center, then sync the site.</t>
   </si>
   <si>
-    <t>MASTER WORKBOOK | LAST SYNC 2026-04-27 19:01:16 UTC | CTRL+CLICK LINKS TO NAVIGATE</t>
+    <t>MASTER WORKBOOK | LAST SYNC 2026-06-21 23:30:24 UTC | CTRL+CLICK LINKS TO NAVIGATE</t>
   </si>
   <si>
     <t>Use the cards below for primary editing, the workflow panel for the sync cycle, and the grouped panels at the bottom for advanced sheets.</t>
@@ -223,7 +223,7 @@
     <t>Editing rules, shortcuts, and the quickest path to each content area.</t>
   </si>
   <si>
-    <t>GUIDE SHEET | LAST SYNC 2026-04-27 19:01:16 UTC | START FROM HOME FOR THE FASTEST FLOW</t>
+    <t>GUIDE SHEET | LAST SYNC 2026-06-21 23:30:24 UTC | START FROM HOME FOR THE FASTEST FLOW</t>
   </si>
   <si>
     <t>Back to HOME</t>
@@ -584,7 +584,7 @@
     <t>Identity, bio headline, social links, and testimonial section copy.</t>
   </si>
   <si>
-    <t>PRIMARY EDIT SURFACE | LAST SYNC 2026-04-27 19:01:16 UTC</t>
+    <t>PRIMARY EDIT SURFACE | LAST SYNC 2026-06-21 23:30:24 UTC</t>
   </si>
   <si>
     <t>Guide</t>
@@ -650,7 +650,7 @@
     <t>Alberto Medina Garcia</t>
   </si>
   <si>
-    <t>Full-Stack Developer &amp; Automation Engineer</t>
+    <t>Full-Stack Systems &amp; Automation Engineer</t>
   </si>
   <si>
     <t>I build reliable products, automation workflows, and AI systems with clear product thinking.</t>
@@ -662,7 +662,7 @@
     <t>AI Philosophy</t>
   </si>
   <si>
-    <t>AI does not replace good engineers. It exposes weak ones. The value is not in using it, but in knowing how to think with it, control it, and build reliable systems around it.</t>
+    <t>AI amplifies engineering judgment. The real value comes from framing the problem well, controlling the system, and making the result reliable in production.</t>
   </si>
   <si>
     <t>https://github.com/Albjav12345</t>
@@ -716,7 +716,7 @@
     <t>buttonCvHref</t>
   </si>
   <si>
-    <t>SYSTEMS / AUTOMATION / AI</t>
+    <t>FULL-STACK SYSTEMS / AUTOMATION / AI</t>
   </si>
   <si>
     <t>ALBERTO</t>
@@ -728,16 +728,16 @@
     <t>@Albjav12345</t>
   </si>
   <si>
-    <t>I build full-stack products, automation workflows, and AI systems that solve real operational problems and still feel polished to use.</t>
+    <t>I design and ship full-stack products, automation workflows, and AI systems—from polished interfaces to reliable backend operations.</t>
   </si>
   <si>
     <t>ACCESS_TERMINAL</t>
   </si>
   <si>
-    <t>GET_MANIFEST.PDF</t>
-  </si>
-  <si>
-    <t>MANIFEST_PENDING</t>
+    <t>DOWNLOAD_CV.PDF</t>
+  </si>
+  <si>
+    <t>CV_PENDING</t>
   </si>
   <si>
     <t>/manifest-test.pdf</t>
@@ -797,10 +797,10 @@
     <t>enabled</t>
   </si>
   <si>
-    <t>Unity Developer</t>
-  </si>
-  <si>
-    <t>High-Fidelity Unity UX</t>
+    <t>Unity Interface Systems</t>
+  </si>
+  <si>
+    <t>High-Fidelity Real-Time UX</t>
   </si>
   <si>
     <t>A lot of developers can build tools. Far fewer can build custom interfaces that feel intentional inside a real-time engine.</t>
@@ -830,10 +830,10 @@
     <t>https://github.com/Albjav12345/zero_touch_email_bot</t>
   </si>
   <si>
-    <t>Paddle Booking App</t>
-  </si>
-  <si>
-    <t>Reactive State &amp; Live Synchronization</t>
+    <t>Padel Booking Platform</t>
+  </si>
+  <si>
+    <t>Live Availability &amp; Conflict-Free Booking</t>
   </si>
   <si>
     <t>Manual booking created conflicts, stale availability, and too much back-and-forth for users.</t>
@@ -860,16 +860,16 @@
     <t>https://github.com/Albjav12345/Fortnite-Lobby-Stream-Finder</t>
   </si>
   <si>
-    <t>USB Exfiltration</t>
-  </si>
-  <si>
-    <t>Adversary Emulation &amp; Headless Acquisition</t>
-  </si>
-  <si>
-    <t>Red team USB collection often fails because of file locks, user friction, and the need to stay quiet on the host.</t>
-  </si>
-  <si>
-    <t>I built a stealth-focused Windows payload for controlled security research, combining native WMI polling and low-friction background collection.</t>
+    <t>Authorized USB Acquisition Lab</t>
+  </si>
+  <si>
+    <t>Controlled Security Research &amp; Endpoint Automation</t>
+  </si>
+  <si>
+    <t>Authorized endpoint collection can fail because of file locks, manual steps, and inconsistent evidence handling during controlled security exercises.</t>
+  </si>
+  <si>
+    <t>I built a Windows-based acquisition workflow for authorized lab and red-team scenarios, combining native system polling, explicit operator controls, and low-friction evidence collection.</t>
   </si>
   <si>
     <t>https://github.com/Albjav12345/Automated-USB-Exfiltration</t>
@@ -1223,7 +1223,7 @@
     <t>BUILD.</t>
   </si>
   <si>
-    <t>If you already know what you want to build, we can scope it properly. If not, we can start from the problem and work forward.</t>
+    <t>For product engineering roles, freelance builds, or systems work, share the context and the outcome you need. We can scope the next step from there.</t>
   </si>
   <si>
     <t>Primary_Contact</t>
@@ -1307,7 +1307,7 @@
     <t>previewLink</t>
   </si>
   <si>
-    <t>/assets/alberto.png</t>
+    <t>/assets/alberto.webp</t>
   </si>
   <si>
     <t>Alberto Medina Garcia avatar</t>
@@ -1328,7 +1328,7 @@
     <t>Unity Developer master video source</t>
   </si>
   <si>
-    <t>Unity Developer video</t>
+    <t>Unity Interface Systems video</t>
   </si>
   <si>
     <t>/assets/projects/visual-interfaces.png</t>
@@ -1340,6 +1340,9 @@
     <t>Unity Developer poster image</t>
   </si>
   <si>
+    <t>Unity Interface Systems thumbnail</t>
+  </si>
+  <si>
     <t>/assets/projects/unity.webp</t>
   </si>
   <si>
@@ -1349,6 +1352,9 @@
     <t>Unity Developer icon asset</t>
   </si>
   <si>
+    <t>Unity Interface Systems icon</t>
+  </si>
+  <si>
     <t>/assets/projects/zero-touch-ai.mp4</t>
   </si>
   <si>
@@ -1388,7 +1394,7 @@
     <t>Paddle Booking App master video source</t>
   </si>
   <si>
-    <t>Paddle Booking App video</t>
+    <t>Padel Booking Platform video</t>
   </si>
   <si>
     <t>/assets/projects/padel-booking.png</t>
@@ -1400,6 +1406,9 @@
     <t>Paddle Booking App poster image</t>
   </si>
   <si>
+    <t>Padel Booking Platform thumbnail</t>
+  </si>
+  <si>
     <t>/assets/projects/padel-booking-logo.png</t>
   </si>
   <si>
@@ -1409,6 +1418,9 @@
     <t>Paddle Booking App icon asset</t>
   </si>
   <si>
+    <t>Padel Booking Platform icon</t>
+  </si>
+  <si>
     <t>/assets/projects/twitch-live.mp4</t>
   </si>
   <si>
@@ -1448,7 +1460,7 @@
     <t>USB Exfiltration master video source</t>
   </si>
   <si>
-    <t>USB Exfiltration video</t>
+    <t>Authorized USB Acquisition Lab video</t>
   </si>
   <si>
     <t>/assets/projects/usb-extraction.png</t>
@@ -1460,6 +1472,9 @@
     <t>USB Exfiltration poster image</t>
   </si>
   <si>
+    <t>Authorized USB Acquisition Lab thumbnail</t>
+  </si>
+  <si>
     <t>/assets/projects/terminal.ico</t>
   </si>
   <si>
@@ -1469,6 +1484,9 @@
     <t>USB Exfiltration icon asset</t>
   </si>
   <si>
+    <t>Authorized USB Acquisition Lab icon</t>
+  </si>
+  <si>
     <t>/assets/testimonials/client3.png</t>
   </si>
   <si>
@@ -1613,7 +1631,7 @@
     <t>Brand lockup and terminal button label.</t>
   </si>
   <si>
-    <t>ADVANCED DATA SHEET | LAST SYNC 2026-04-27 19:01:16 UTC</t>
+    <t>ADVANCED DATA SHEET | LAST SYNC 2026-06-21 23:30:24 UTC</t>
   </si>
   <si>
     <t>Supporting data sheet. Changes here feed one or more primary editing surfaces.</t>
@@ -1757,16 +1775,16 @@
     <t>Small metadata chips shown in the landing hero.</t>
   </si>
   <si>
-    <t>Stack_Focus</t>
-  </si>
-  <si>
-    <t>PYTHON / REACT / UNITY</t>
-  </si>
-  <si>
-    <t>Exp_Runtime</t>
-  </si>
-  <si>
-    <t>5+ YEARS SHIPPING</t>
+    <t>Delivery_Focus</t>
+  </si>
+  <si>
+    <t>PRODUCTS / AUTOMATION / AI</t>
+  </si>
+  <si>
+    <t>Work_Mode</t>
+  </si>
+  <si>
+    <t>SPAIN / REMOTE</t>
   </si>
   <si>
     <t>Terminal shell labels and tooltip copy.</t>
@@ -1883,10 +1901,10 @@
     <t>SYS_02</t>
   </si>
   <si>
-    <t>Personal</t>
-  </si>
-  <si>
-    <t>Projects.</t>
+    <t>Selected</t>
+  </si>
+  <si>
+    <t>Systems.</t>
   </si>
   <si>
     <t>SYS_03</t>
@@ -2190,9 +2208,6 @@
   </si>
   <si>
     <t>System Status: All Systems Operational</t>
-  </si>
-  <si>
-    <t>SPAIN / REMOTE</t>
   </si>
   <si>
     <t>AUTO_PORT_V2.0</t>
@@ -4195,7 +4210,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -4223,7 +4238,7 @@
         <v>177</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
@@ -4277,7 +4292,7 @@
         <v>406</v>
       </c>
       <c r="C8" s="89" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D8" s="88" t="s">
         <v>412</v>
@@ -4307,7 +4322,7 @@
       </c>
       <c r="D9" s="91" t="str">
         <f>IF('ASSETS'!$A9="","",'ASSETS'!$I9)</f>
-        <v>/assets/alberto.png</v>
+        <v>/assets/alberto.webp</v>
       </c>
       <c r="E9" s="91" t="str">
         <f>IF('ASSETS'!$A9="","",'ASSETS'!$L9)</f>
@@ -5715,7 +5730,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -5724,7 +5739,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -5748,7 +5763,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -5781,16 +5796,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E8" s="66" t="s">
         <v>196</v>
@@ -5798,16 +5813,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C9" s="67" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E9" s="70" t="s">
         <v>207</v>
@@ -5938,7 +5953,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -5948,7 +5963,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -5974,7 +5989,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -6016,7 +6031,7 @@
         <v>185</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>246</v>
@@ -6030,13 +6045,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D9" s="76" t="s">
         <v>98</v>
@@ -6045,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6053,10 +6068,10 @@
         <v>111</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D10" s="78" t="s">
         <v>98</v>
@@ -6065,7 +6080,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6073,10 +6088,10 @@
         <v>123</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D11" s="76" t="s">
         <v>98</v>
@@ -6085,18 +6100,18 @@
         <v>3</v>
       </c>
       <c r="F11" s="70" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="71" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D12" s="78" t="s">
         <v>98</v>
@@ -6105,7 +6120,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="70" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6113,10 +6128,10 @@
         <v>140</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D13" s="76" t="s">
         <v>112</v>
@@ -6125,18 +6140,18 @@
         <v>5</v>
       </c>
       <c r="F13" s="70" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="71" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B14" s="71" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="71" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D14" s="78" t="s">
         <v>98</v>
@@ -6145,7 +6160,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="70" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6294,7 +6309,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -6302,7 +6317,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -6324,7 +6339,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -6354,10 +6369,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>245</v>
@@ -6368,10 +6383,10 @@
     </row>
     <row r="9" ht="68" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -6382,10 +6397,10 @@
     </row>
     <row r="10" ht="68" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -6514,7 +6529,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -6523,7 +6538,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -6547,7 +6562,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -6586,7 +6601,7 @@
         <v>371</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>245</v>
@@ -6600,10 +6615,10 @@
         <v>123</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D9" s="67">
         <v>1</v>
@@ -6614,13 +6629,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D10" s="71">
         <v>2</v>
@@ -6631,13 +6646,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D11" s="67">
         <v>3</v>
@@ -6648,13 +6663,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="71" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D12" s="71">
         <v>4</v>
@@ -6792,7 +6807,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -6800,7 +6815,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -6820,7 +6835,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -6853,7 +6868,7 @@
         <v>371</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>245</v>
@@ -6864,10 +6879,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -6878,10 +6893,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -7009,7 +7024,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -7019,7 +7034,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -7045,7 +7060,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7081,19 +7096,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E8" s="65" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F8" s="66" t="s">
         <v>196</v>
@@ -7101,19 +7116,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="F9" s="70" t="s">
         <v>207</v>
@@ -7253,7 +7268,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -7262,7 +7277,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -7286,7 +7301,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7319,13 +7334,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>245</v>
@@ -7339,7 +7354,7 @@
         <v>105</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C9" s="67" t="s">
         <v>104</v>
@@ -7348,7 +7363,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7356,7 +7371,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C10" s="71" t="s">
         <v>127</v>
@@ -7365,7 +7380,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7373,7 +7388,7 @@
         <v>105</v>
       </c>
       <c r="B11" s="68" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>116</v>
@@ -7382,7 +7397,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7390,7 +7405,7 @@
         <v>105</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>116</v>
@@ -7399,7 +7414,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7407,7 +7422,7 @@
         <v>105</v>
       </c>
       <c r="B13" s="68" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C13" s="67" t="s">
         <v>135</v>
@@ -7416,7 +7431,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7424,7 +7439,7 @@
         <v>105</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C14" s="71" t="s">
         <v>104</v>
@@ -7433,7 +7448,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -7441,7 +7456,7 @@
         <v>105</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C15" s="67" t="s">
         <v>127</v>
@@ -7450,7 +7465,7 @@
         <v>7</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -7458,7 +7473,7 @@
         <v>117</v>
       </c>
       <c r="B16" s="72" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C16" s="71" t="s">
         <v>104</v>
@@ -7467,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -7475,7 +7490,7 @@
         <v>117</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C17" s="67" t="s">
         <v>104</v>
@@ -7484,7 +7499,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -7654,14 +7669,14 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -7704,7 +7719,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>245</v>
@@ -7715,7 +7730,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B9" s="67">
         <v>1</v>
@@ -7726,7 +7741,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="72" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B10" s="71">
         <v>2</v>
@@ -7737,7 +7752,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B11" s="67">
         <v>3</v>
@@ -7748,7 +7763,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B12" s="71">
         <v>4</v>
@@ -7875,7 +7890,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -7885,7 +7900,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -7909,7 +7924,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7945,16 +7960,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>233</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="E8" s="65" t="s">
         <v>245</v>
@@ -7968,13 +7983,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E9" s="67">
         <v>1</v>
@@ -7988,13 +8003,13 @@
         <v>123</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="E10" s="71">
         <v>2</v>
@@ -8008,13 +8023,13 @@
         <v>132</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="E11" s="67">
         <v>3</v>
@@ -8028,13 +8043,13 @@
         <v>140</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="E12" s="71">
         <v>4</v>
@@ -8048,13 +8063,13 @@
         <v>143</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E13" s="67">
         <v>5</v>
@@ -8790,7 +8805,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -8800,7 +8815,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -8824,7 +8839,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -8860,7 +8875,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>234</v>
@@ -8869,7 +8884,7 @@
         <v>125</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="E8" s="65" t="s">
         <v>245</v>
@@ -8883,7 +8898,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C9" s="67" t="s">
         <v>106</v>
@@ -8903,7 +8918,7 @@
         <v>122</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="C10" s="71" t="s">
         <v>118</v>
@@ -8923,7 +8938,7 @@
         <v>131</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>128</v>
@@ -8943,7 +8958,7 @@
         <v>139</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>136</v>
@@ -9109,7 +9124,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -9117,7 +9132,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -9137,7 +9152,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -9167,7 +9182,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>371</v>
@@ -9184,7 +9199,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -9198,7 +9213,7 @@
         <v>110</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -9212,7 +9227,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C11" s="67">
         <v>3</v>
@@ -9226,7 +9241,7 @@
         <v>110</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C12" s="71">
         <v>4</v>
@@ -9240,7 +9255,7 @@
         <v>110</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C13" s="67">
         <v>5</v>
@@ -9254,7 +9269,7 @@
         <v>110</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C14" s="71">
         <v>6</v>
@@ -9268,7 +9283,7 @@
         <v>122</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C15" s="67">
         <v>1</v>
@@ -9282,7 +9297,7 @@
         <v>122</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C16" s="71">
         <v>2</v>
@@ -9296,7 +9311,7 @@
         <v>122</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C17" s="67">
         <v>3</v>
@@ -9310,7 +9325,7 @@
         <v>122</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C18" s="71">
         <v>4</v>
@@ -9324,7 +9339,7 @@
         <v>122</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C19" s="67">
         <v>5</v>
@@ -9338,7 +9353,7 @@
         <v>131</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C20" s="71">
         <v>1</v>
@@ -9352,7 +9367,7 @@
         <v>131</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C21" s="67">
         <v>2</v>
@@ -9366,7 +9381,7 @@
         <v>131</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C22" s="71">
         <v>3</v>
@@ -9380,7 +9395,7 @@
         <v>131</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C23" s="67">
         <v>4</v>
@@ -9394,7 +9409,7 @@
         <v>131</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C24" s="71">
         <v>5</v>
@@ -9408,7 +9423,7 @@
         <v>139</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C25" s="67">
         <v>1</v>
@@ -9422,7 +9437,7 @@
         <v>139</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C26" s="71">
         <v>2</v>
@@ -9436,7 +9451,7 @@
         <v>139</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C27" s="67">
         <v>3</v>
@@ -9450,7 +9465,7 @@
         <v>139</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C28" s="71">
         <v>4</v>
@@ -9464,7 +9479,7 @@
         <v>139</v>
       </c>
       <c r="B29" s="67" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="C29" s="67">
         <v>5</v>
@@ -9478,7 +9493,7 @@
         <v>139</v>
       </c>
       <c r="B30" s="71" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C30" s="71">
         <v>6</v>
@@ -9646,7 +9661,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -9654,7 +9669,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -9676,7 +9691,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -9706,7 +9721,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>371</v>
@@ -9723,7 +9738,7 @@
         <v>99</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -9737,7 +9752,7 @@
         <v>99</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -9751,7 +9766,7 @@
         <v>99</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C11" s="67">
         <v>3</v>
@@ -9765,7 +9780,7 @@
         <v>99</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C12" s="71">
         <v>4</v>
@@ -9779,7 +9794,7 @@
         <v>113</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C13" s="67">
         <v>1</v>
@@ -9793,7 +9808,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C14" s="71">
         <v>2</v>
@@ -9807,7 +9822,7 @@
         <v>113</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C15" s="67">
         <v>3</v>
@@ -9821,7 +9836,7 @@
         <v>113</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C16" s="71">
         <v>4</v>
@@ -9835,7 +9850,7 @@
         <v>124</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C17" s="67">
         <v>1</v>
@@ -9849,7 +9864,7 @@
         <v>124</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C18" s="71">
         <v>2</v>
@@ -9863,7 +9878,7 @@
         <v>124</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C19" s="67">
         <v>3</v>
@@ -9877,7 +9892,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C20" s="71">
         <v>4</v>
@@ -9891,7 +9906,7 @@
         <v>133</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C21" s="67">
         <v>1</v>
@@ -9905,7 +9920,7 @@
         <v>133</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C22" s="71">
         <v>2</v>
@@ -9919,7 +9934,7 @@
         <v>133</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C23" s="67">
         <v>3</v>
@@ -9933,7 +9948,7 @@
         <v>133</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C24" s="71">
         <v>4</v>
@@ -9947,7 +9962,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C25" s="67">
         <v>1</v>
@@ -9961,7 +9976,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C26" s="71">
         <v>2</v>
@@ -9975,7 +9990,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C27" s="67">
         <v>3</v>
@@ -9989,7 +10004,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C28" s="71">
         <v>4</v>
@@ -10166,7 +10181,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -10174,7 +10189,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -10196,7 +10211,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -10226,7 +10241,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>371</v>
@@ -10243,7 +10258,7 @@
         <v>99</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -10257,7 +10272,7 @@
         <v>99</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -10271,7 +10286,7 @@
         <v>99</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C11" s="67">
         <v>3</v>
@@ -10285,7 +10300,7 @@
         <v>99</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="C12" s="71">
         <v>4</v>
@@ -10299,7 +10314,7 @@
         <v>113</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C13" s="67">
         <v>1</v>
@@ -10313,7 +10328,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C14" s="71">
         <v>2</v>
@@ -10327,7 +10342,7 @@
         <v>113</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C15" s="67">
         <v>3</v>
@@ -10341,7 +10356,7 @@
         <v>113</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C16" s="71">
         <v>4</v>
@@ -10355,7 +10370,7 @@
         <v>124</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C17" s="67">
         <v>1</v>
@@ -10369,7 +10384,7 @@
         <v>124</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="C18" s="71">
         <v>2</v>
@@ -10383,7 +10398,7 @@
         <v>124</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C19" s="67">
         <v>3</v>
@@ -10397,7 +10412,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C20" s="71">
         <v>4</v>
@@ -10411,7 +10426,7 @@
         <v>133</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C21" s="67">
         <v>1</v>
@@ -10425,7 +10440,7 @@
         <v>133</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C22" s="71">
         <v>2</v>
@@ -10439,7 +10454,7 @@
         <v>133</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C23" s="67">
         <v>3</v>
@@ -10453,7 +10468,7 @@
         <v>133</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="C24" s="71">
         <v>4</v>
@@ -10467,7 +10482,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="C25" s="67">
         <v>1</v>
@@ -10481,7 +10496,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C26" s="71">
         <v>2</v>
@@ -10495,7 +10510,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C27" s="67">
         <v>3</v>
@@ -10509,7 +10524,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C28" s="71">
         <v>4</v>
@@ -10691,7 +10706,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -10702,7 +10717,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -10728,7 +10743,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -10770,7 +10785,7 @@
         <v>276</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>371</v>
@@ -10779,7 +10794,7 @@
         <v>278</v>
       </c>
       <c r="E8" s="65" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F8" s="65" t="s">
         <v>245</v>
@@ -10793,16 +10808,16 @@
         <v>108</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="F9" s="67">
         <v>1</v>
@@ -10816,16 +10831,16 @@
         <v>120</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="F10" s="71">
         <v>2</v>
@@ -10988,7 +11003,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -10998,7 +11013,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -11024,7 +11039,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -11063,7 +11078,7 @@
         <v>185</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>125</v>
@@ -11080,7 +11095,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B9" s="67" t="s">
         <v>203</v>
@@ -11100,7 +11115,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B10" s="71" t="s">
         <v>204</v>
@@ -11120,10 +11135,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>129</v>
@@ -11143,7 +11158,7 @@
         <v>137</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>137</v>
@@ -11311,7 +11326,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -11320,7 +11335,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -11346,7 +11361,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -11382,10 +11397,10 @@
         <v>371</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>245</v>
@@ -11396,13 +11411,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="D9" s="67">
         <v>1</v>
@@ -11413,10 +11428,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C10" s="71" t="s">
         <v>252</v>
@@ -11430,10 +11445,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>252</v>
@@ -11576,7 +11591,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -11585,7 +11600,7 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" s="94"/>
       <c r="C3" s="94"/>
@@ -11607,7 +11622,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -11643,13 +11658,13 @@
         <v>185</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E8" s="66" t="s">
         <v>196</v>
@@ -11660,13 +11675,13 @@
         <v>197</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>712</v>
+        <v>576</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="E9" s="70" t="s">
         <v>207</v>
@@ -13342,7 +13357,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="13" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="68" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
         <v>5</v>
       </c>
@@ -16010,7 +16025,7 @@
       </c>
       <c r="I9" s="83" t="str">
         <f>IF($A9="","",IF(UPPER($H9)&lt;&gt;"TRUE","",IF($C9="import_local",IF($E9&lt;&gt;"",$E9,""),IF($C9="external_url",$D9,IF(IF($D9&lt;&gt;"",$D9,$E9)&lt;&gt;"",IF($D9&lt;&gt;"",$D9,$E9),"")))))</f>
-        <v>/assets/alberto.png</v>
+        <v>/assets/alberto.webp</v>
       </c>
       <c r="J9" s="24" t="str">
         <f>IF($A9="","",IF(UPPER($H9)&lt;&gt;"TRUE","Disabled",HYPERLINK("http://127.0.0.1:5173/__dev/asset-source"&amp;"?assetId="&amp;ENCODEURL($A9)&amp;"&amp;sig="&amp;ENCODEURL($B9&amp;"|"&amp;$C9&amp;"|"&amp;$D9&amp;"|"&amp;$E9&amp;"|"&amp;$H9),"Open source")))</f>
@@ -16029,7 +16044,7 @@
       </c>
       <c r="N9" s="85" t="str">
         <f>IF($A9="","",IF(UPPER($H9)&lt;&gt;"TRUE","DISABLED",IF($C9="external_url",IF(OR(LEFT(LOWER($D9),7)="http://",LEFT(LOWER($D9),8)="https://"),"READY -&gt; "&amp;$I9,"NEEDS HTTP URL"),IF($C9="import_local",IF($D9="","NEEDS SOURCE FILE",IF($E9="","NEEDS TARGET PATH","READY -&gt; "&amp;$I9)),IF($C9="existing_public",IF(IF($D9&lt;&gt;"",$D9,$E9)&lt;&gt;"","READY -&gt; "&amp;$I9,"NEEDS PUBLIC PATH"),"CHECK MODE")))))</f>
-        <v>READY -&gt; /assets/alberto.png</v>
+        <v>READY -&gt; /assets/alberto.webp</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -16119,7 +16134,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L11" s="84" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M11" s="24" t="str">
         <f>IF($A11="","",HYPERLINK("#'ASSET_PREVIEW'!A11","Open preview"))</f>
@@ -16141,16 +16156,16 @@
         <v>101</v>
       </c>
       <c r="D12" s="72" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E12" s="72" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F12" s="71" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G12" s="72" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H12" s="78" t="s">
         <v>98</v>
@@ -16168,7 +16183,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L12" s="84" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M12" s="24" t="str">
         <f>IF($A12="","",HYPERLINK("#'ASSET_PREVIEW'!A12","Open preview"))</f>
@@ -16190,16 +16205,16 @@
         <v>101</v>
       </c>
       <c r="D13" s="68" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G13" s="68" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H13" s="76" t="s">
         <v>98</v>
@@ -16217,7 +16232,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L13" s="84" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M13" s="24" t="str">
         <f>IF($A13="","",HYPERLINK("#'ASSET_PREVIEW'!A13","Open preview"))</f>
@@ -16239,16 +16254,16 @@
         <v>101</v>
       </c>
       <c r="D14" s="72" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E14" s="72" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F14" s="71" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G14" s="72" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H14" s="78" t="s">
         <v>98</v>
@@ -16266,7 +16281,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L14" s="84" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M14" s="24" t="str">
         <f>IF($A14="","",HYPERLINK("#'ASSET_PREVIEW'!A14","Open preview"))</f>
@@ -16288,16 +16303,16 @@
         <v>101</v>
       </c>
       <c r="D15" s="68" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F15" s="67" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H15" s="76" t="s">
         <v>98</v>
@@ -16315,7 +16330,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L15" s="84" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M15" s="24" t="str">
         <f>IF($A15="","",HYPERLINK("#'ASSET_PREVIEW'!A15","Open preview"))</f>
@@ -16337,16 +16352,16 @@
         <v>101</v>
       </c>
       <c r="D16" s="72" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E16" s="72" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F16" s="71" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G16" s="72" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H16" s="78" t="s">
         <v>98</v>
@@ -16364,7 +16379,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L16" s="84" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M16" s="24" t="str">
         <f>IF($A16="","",HYPERLINK("#'ASSET_PREVIEW'!A16","Open preview"))</f>
@@ -16386,16 +16401,16 @@
         <v>101</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E17" s="68" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F17" s="67" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G17" s="68" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H17" s="76" t="s">
         <v>98</v>
@@ -16413,7 +16428,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L17" s="84" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M17" s="24" t="str">
         <f>IF($A17="","",HYPERLINK("#'ASSET_PREVIEW'!A17","Open preview"))</f>
@@ -16435,16 +16450,16 @@
         <v>101</v>
       </c>
       <c r="D18" s="72" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F18" s="71" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H18" s="78" t="s">
         <v>98</v>
@@ -16462,7 +16477,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L18" s="84" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M18" s="24" t="str">
         <f>IF($A18="","",HYPERLINK("#'ASSET_PREVIEW'!A18","Open preview"))</f>
@@ -16484,16 +16499,16 @@
         <v>101</v>
       </c>
       <c r="D19" s="68" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="H19" s="76" t="s">
         <v>98</v>
@@ -16511,7 +16526,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L19" s="84" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M19" s="24" t="str">
         <f>IF($A19="","",HYPERLINK("#'ASSET_PREVIEW'!A19","Open preview"))</f>
@@ -16533,16 +16548,16 @@
         <v>101</v>
       </c>
       <c r="D20" s="72" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E20" s="72" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F20" s="71" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G20" s="72" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H20" s="78" t="s">
         <v>98</v>
@@ -16560,7 +16575,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L20" s="84" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M20" s="24" t="str">
         <f>IF($A20="","",HYPERLINK("#'ASSET_PREVIEW'!A20","Open preview"))</f>
@@ -16582,16 +16597,16 @@
         <v>101</v>
       </c>
       <c r="D21" s="68" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F21" s="67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H21" s="76" t="s">
         <v>98</v>
@@ -16609,7 +16624,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L21" s="84" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M21" s="24" t="str">
         <f>IF($A21="","",HYPERLINK("#'ASSET_PREVIEW'!A21","Open preview"))</f>
@@ -16631,16 +16646,16 @@
         <v>101</v>
       </c>
       <c r="D22" s="72" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E22" s="72" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F22" s="71" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G22" s="72" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H22" s="78" t="s">
         <v>98</v>
@@ -16658,7 +16673,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L22" s="84" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M22" s="24" t="str">
         <f>IF($A22="","",HYPERLINK("#'ASSET_PREVIEW'!A22","Open preview"))</f>
@@ -16680,16 +16695,16 @@
         <v>101</v>
       </c>
       <c r="D23" s="68" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H23" s="76" t="s">
         <v>98</v>
@@ -16707,7 +16722,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L23" s="84" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="M23" s="24" t="str">
         <f>IF($A23="","",HYPERLINK("#'ASSET_PREVIEW'!A23","Open preview"))</f>
@@ -16729,16 +16744,16 @@
         <v>101</v>
       </c>
       <c r="D24" s="72" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="H24" s="78" t="s">
         <v>98</v>
@@ -16756,7 +16771,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L24" s="84" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="M24" s="24" t="str">
         <f>IF($A24="","",HYPERLINK("#'ASSET_PREVIEW'!A24","Open preview"))</f>
@@ -16778,16 +16793,16 @@
         <v>101</v>
       </c>
       <c r="D25" s="68" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F25" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="H25" s="76" t="s">
         <v>98</v>
@@ -16805,7 +16820,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L25" s="84" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="M25" s="24" t="str">
         <f>IF($A25="","",HYPERLINK("#'ASSET_PREVIEW'!A25","Open preview"))</f>
@@ -16827,16 +16842,16 @@
         <v>101</v>
       </c>
       <c r="D26" s="72" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E26" s="72" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G26" s="72" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="H26" s="78" t="s">
         <v>98</v>
@@ -16854,7 +16869,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L26" s="84" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="M26" s="24" t="str">
         <f>IF($A26="","",HYPERLINK("#'ASSET_PREVIEW'!A26","Open preview"))</f>
@@ -16876,16 +16891,16 @@
         <v>101</v>
       </c>
       <c r="D27" s="68" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E27" s="68" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F27" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G27" s="68" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="H27" s="76" t="s">
         <v>98</v>
@@ -16903,7 +16918,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L27" s="84" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="M27" s="24" t="str">
         <f>IF($A27="","",HYPERLINK("#'ASSET_PREVIEW'!A27","Open preview"))</f>
@@ -16925,16 +16940,16 @@
         <v>101</v>
       </c>
       <c r="D28" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="E28" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="F28" s="71" t="s">
+        <v>478</v>
+      </c>
+      <c r="G28" s="72" t="s">
         <v>479</v>
-      </c>
-      <c r="E28" s="72" t="s">
-        <v>479</v>
-      </c>
-      <c r="F28" s="71" t="s">
-        <v>472</v>
-      </c>
-      <c r="G28" s="72" t="s">
-        <v>473</v>
       </c>
       <c r="H28" s="78" t="s">
         <v>98</v>
@@ -16952,7 +16967,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L28" s="84" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="M28" s="24" t="str">
         <f>IF($A28="","",HYPERLINK("#'ASSET_PREVIEW'!A28","Open preview"))</f>
@@ -16974,16 +16989,16 @@
         <v>101</v>
       </c>
       <c r="D29" s="68" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F29" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G29" s="68" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H29" s="76" t="s">
         <v>98</v>
@@ -17001,7 +17016,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L29" s="84" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="M29" s="24" t="str">
         <f>IF($A29="","",HYPERLINK("#'ASSET_PREVIEW'!A29","Open preview"))</f>
@@ -17023,16 +17038,16 @@
         <v>101</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E30" s="72" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F30" s="71" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G30" s="72" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H30" s="78" t="s">
         <v>98</v>
@@ -17050,7 +17065,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L30" s="84" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="M30" s="24" t="str">
         <f>IF($A30="","",HYPERLINK("#'ASSET_PREVIEW'!A30","Open preview"))</f>
@@ -17072,16 +17087,16 @@
         <v>101</v>
       </c>
       <c r="D31" s="68" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F31" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G31" s="68" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H31" s="76" t="s">
         <v>98</v>
@@ -17099,7 +17114,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L31" s="84" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="M31" s="24" t="str">
         <f>IF($A31="","",HYPERLINK("#'ASSET_PREVIEW'!A31","Open preview"))</f>
@@ -17121,16 +17136,16 @@
         <v>101</v>
       </c>
       <c r="D32" s="72" t="s">
+        <v>494</v>
+      </c>
+      <c r="E32" s="72" t="s">
+        <v>494</v>
+      </c>
+      <c r="F32" s="71" t="s">
+        <v>478</v>
+      </c>
+      <c r="G32" s="72" t="s">
         <v>488</v>
-      </c>
-      <c r="E32" s="72" t="s">
-        <v>488</v>
-      </c>
-      <c r="F32" s="71" t="s">
-        <v>472</v>
-      </c>
-      <c r="G32" s="72" t="s">
-        <v>482</v>
       </c>
       <c r="H32" s="78" t="s">
         <v>98</v>
@@ -17148,7 +17163,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L32" s="84" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="M32" s="24" t="str">
         <f>IF($A32="","",HYPERLINK("#'ASSET_PREVIEW'!A32","Open preview"))</f>
@@ -17170,16 +17185,16 @@
         <v>101</v>
       </c>
       <c r="D33" s="68" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F33" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G33" s="68" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H33" s="76" t="s">
         <v>98</v>
@@ -17197,7 +17212,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L33" s="86" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M33" s="24" t="str">
         <f>IF($A33="","",HYPERLINK("#'ASSET_PREVIEW'!A33","Open preview"))</f>
@@ -17219,16 +17234,16 @@
         <v>101</v>
       </c>
       <c r="D34" s="72" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E34" s="72" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F34" s="71" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G34" s="72" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H34" s="78" t="s">
         <v>98</v>
@@ -17246,7 +17261,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L34" s="86" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M34" s="24" t="str">
         <f>IF($A34="","",HYPERLINK("#'ASSET_PREVIEW'!A34","Open preview"))</f>
@@ -17268,16 +17283,16 @@
         <v>101</v>
       </c>
       <c r="D35" s="68" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E35" s="68" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F35" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G35" s="68" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H35" s="76" t="s">
         <v>98</v>
@@ -17295,7 +17310,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L35" s="84" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="M35" s="24" t="str">
         <f>IF($A35="","",HYPERLINK("#'ASSET_PREVIEW'!A35","Open preview"))</f>
@@ -17317,16 +17332,16 @@
         <v>101</v>
       </c>
       <c r="D36" s="72" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E36" s="72" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F36" s="71" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G36" s="72" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="H36" s="78" t="s">
         <v>98</v>
@@ -17344,7 +17359,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L36" s="84" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="M36" s="24" t="str">
         <f>IF($A36="","",HYPERLINK("#'ASSET_PREVIEW'!A36","Open preview"))</f>
@@ -17366,16 +17381,16 @@
         <v>101</v>
       </c>
       <c r="D37" s="68" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E37" s="68" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F37" s="67" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G37" s="68" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="H37" s="76" t="s">
         <v>98</v>
@@ -17393,7 +17408,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L37" s="84" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="M37" s="24" t="str">
         <f>IF($A37="","",HYPERLINK("#'ASSET_PREVIEW'!A37","Open preview"))</f>
@@ -17415,16 +17430,16 @@
         <v>101</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E38" s="72" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F38" s="71" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G38" s="72" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="H38" s="78" t="s">
         <v>98</v>
@@ -17442,7 +17457,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L38" s="84" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="M38" s="24" t="str">
         <f>IF($A38="","",HYPERLINK("#'ASSET_PREVIEW'!A38","Open preview"))</f>
@@ -17464,16 +17479,16 @@
         <v>101</v>
       </c>
       <c r="D39" s="68" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F39" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G39" s="68" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="H39" s="76" t="s">
         <v>98</v>
@@ -17491,7 +17506,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L39" s="84" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="M39" s="24" t="str">
         <f>IF($A39="","",HYPERLINK("#'ASSET_PREVIEW'!A39","Open preview"))</f>
@@ -17513,16 +17528,16 @@
         <v>101</v>
       </c>
       <c r="D40" s="72" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E40" s="72" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F40" s="71" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G40" s="72" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="H40" s="78" t="s">
         <v>98</v>
@@ -17540,7 +17555,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L40" s="84" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="M40" s="24" t="str">
         <f>IF($A40="","",HYPERLINK("#'ASSET_PREVIEW'!A40","Open preview"))</f>
@@ -17562,16 +17577,16 @@
         <v>101</v>
       </c>
       <c r="D41" s="68" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F41" s="67" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G41" s="68" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="H41" s="76" t="s">
         <v>98</v>
@@ -17589,7 +17604,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L41" s="84" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="M41" s="24" t="str">
         <f>IF($A41="","",HYPERLINK("#'ASSET_PREVIEW'!A41","Open preview"))</f>
@@ -17611,16 +17626,16 @@
         <v>101</v>
       </c>
       <c r="D42" s="72" t="s">
+        <v>516</v>
+      </c>
+      <c r="E42" s="72" t="s">
+        <v>516</v>
+      </c>
+      <c r="F42" s="71" t="s">
+        <v>478</v>
+      </c>
+      <c r="G42" s="72" t="s">
         <v>510</v>
-      </c>
-      <c r="E42" s="72" t="s">
-        <v>510</v>
-      </c>
-      <c r="F42" s="71" t="s">
-        <v>472</v>
-      </c>
-      <c r="G42" s="72" t="s">
-        <v>504</v>
       </c>
       <c r="H42" s="78" t="s">
         <v>98</v>
@@ -17638,7 +17653,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L42" s="84" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="M42" s="24" t="str">
         <f>IF($A42="","",HYPERLINK("#'ASSET_PREVIEW'!A42","Open preview"))</f>
@@ -17660,16 +17675,16 @@
         <v>101</v>
       </c>
       <c r="D43" s="68" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G43" s="68" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="H43" s="76" t="s">
         <v>98</v>
@@ -17687,7 +17702,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L43" s="86" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M43" s="24" t="str">
         <f>IF($A43="","",HYPERLINK("#'ASSET_PREVIEW'!A43","Open preview"))</f>
@@ -17709,16 +17724,16 @@
         <v>101</v>
       </c>
       <c r="D44" s="72" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E44" s="72" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="F44" s="71" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G44" s="72" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="H44" s="78" t="s">
         <v>98</v>
@@ -17736,7 +17751,7 @@
         <v>Open resolved</v>
       </c>
       <c r="L44" s="86" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M44" s="24" t="str">
         <f>IF($A44="","",HYPERLINK("#'ASSET_PREVIEW'!A44","Open preview"))</f>
@@ -18186,21 +18201,21 @@
     <hyperlink ref="K4" r:id="rId6" tooltip="Projects -&gt; PROJECTS" location="#'PROJECTS'!A8"/>
     <hyperlink ref="M4" r:id="rId7" tooltip="Testimonials -&gt; TESTIMONIALS" location="#'TESTIMONIALS'!A8"/>
     <hyperlink ref="L9" r:id="rId8" tooltip="Profile avatar -&gt; PROFILE" location="#'PROFILE'!A9"/>
-    <hyperlink ref="L10" r:id="rId9" tooltip="Unity Developer video -&gt; PROJECTS" location="#'PROJECTS'!A9"/>
-    <hyperlink ref="L11" r:id="rId10" tooltip="Unity Developer thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A9"/>
-    <hyperlink ref="L12" r:id="rId11" tooltip="Unity Developer icon -&gt; PROJECTS" location="#'PROJECTS'!A9"/>
+    <hyperlink ref="L10" r:id="rId9" tooltip="Unity Interface Systems video -&gt; PROJECTS" location="#'PROJECTS'!A9"/>
+    <hyperlink ref="L11" r:id="rId10" tooltip="Unity Interface Systems thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A9"/>
+    <hyperlink ref="L12" r:id="rId11" tooltip="Unity Interface Systems icon -&gt; PROJECTS" location="#'PROJECTS'!A9"/>
     <hyperlink ref="L13" r:id="rId12" tooltip="Smart Inbox Manager video -&gt; PROJECTS" location="#'PROJECTS'!A10"/>
     <hyperlink ref="L14" r:id="rId13" tooltip="Smart Inbox Manager thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A10"/>
     <hyperlink ref="L15" r:id="rId14" tooltip="Smart Inbox Manager icon -&gt; PROJECTS" location="#'PROJECTS'!A10"/>
-    <hyperlink ref="L16" r:id="rId15" tooltip="Paddle Booking App video -&gt; PROJECTS" location="#'PROJECTS'!A11"/>
-    <hyperlink ref="L17" r:id="rId16" tooltip="Paddle Booking App thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A11"/>
-    <hyperlink ref="L18" r:id="rId17" tooltip="Paddle Booking App icon -&gt; PROJECTS" location="#'PROJECTS'!A11"/>
+    <hyperlink ref="L16" r:id="rId15" tooltip="Padel Booking Platform video -&gt; PROJECTS" location="#'PROJECTS'!A11"/>
+    <hyperlink ref="L17" r:id="rId16" tooltip="Padel Booking Platform thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A11"/>
+    <hyperlink ref="L18" r:id="rId17" tooltip="Padel Booking Platform icon -&gt; PROJECTS" location="#'PROJECTS'!A11"/>
     <hyperlink ref="L19" r:id="rId18" tooltip="Twitch Live Analytics video -&gt; PROJECTS" location="#'PROJECTS'!A12"/>
     <hyperlink ref="L20" r:id="rId19" tooltip="Twitch Live Analytics thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A12"/>
     <hyperlink ref="L21" r:id="rId20" tooltip="Twitch Live Analytics icon -&gt; PROJECTS" location="#'PROJECTS'!A12"/>
-    <hyperlink ref="L22" r:id="rId21" tooltip="USB Exfiltration video -&gt; PROJECTS" location="#'PROJECTS'!A13"/>
-    <hyperlink ref="L23" r:id="rId22" tooltip="USB Exfiltration thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A13"/>
-    <hyperlink ref="L24" r:id="rId23" tooltip="USB Exfiltration icon -&gt; PROJECTS" location="#'PROJECTS'!A13"/>
+    <hyperlink ref="L22" r:id="rId21" tooltip="Authorized USB Acquisition Lab video -&gt; PROJECTS" location="#'PROJECTS'!A13"/>
+    <hyperlink ref="L23" r:id="rId22" tooltip="Authorized USB Acquisition Lab thumbnail -&gt; PROJECTS" location="#'PROJECTS'!A13"/>
+    <hyperlink ref="L24" r:id="rId23" tooltip="Authorized USB Acquisition Lab icon -&gt; PROJECTS" location="#'PROJECTS'!A13"/>
     <hyperlink ref="L25" r:id="rId24" tooltip="automation-outstanding-work avatar -&gt; TESTIMONIALS" location="#'TESTIMONIALS'!A19"/>
     <hyperlink ref="L26" r:id="rId25" tooltip="unity-great-work avatar -&gt; TESTIMONIALS" location="#'TESTIMONIALS'!A12"/>
     <hyperlink ref="L27" r:id="rId26" tooltip="automation-nice-guy avatar -&gt; TESTIMONIALS" location="#'TESTIMONIALS'!A25"/>

--- a/src/data/content/portfolio-master.xlsx
+++ b/src/data/content/portfolio-master.xlsx
@@ -45,7 +45,7 @@
     <t>Edit the workbook from a single control center, then sync the site.</t>
   </si>
   <si>
-    <t>MASTER WORKBOOK | LAST SYNC 2026-06-21 23:30:24 UTC | CTRL+CLICK LINKS TO NAVIGATE</t>
+    <t>MASTER WORKBOOK | LAST SYNC 2026-06-22 17:47:57 UTC | CTRL+CLICK LINKS TO NAVIGATE</t>
   </si>
   <si>
     <t>Use the cards below for primary editing, the workflow panel for the sync cycle, and the grouped panels at the bottom for advanced sheets.</t>
@@ -223,7 +223,7 @@
     <t>Editing rules, shortcuts, and the quickest path to each content area.</t>
   </si>
   <si>
-    <t>GUIDE SHEET | LAST SYNC 2026-06-21 23:30:24 UTC | START FROM HOME FOR THE FASTEST FLOW</t>
+    <t>GUIDE SHEET | LAST SYNC 2026-06-22 17:47:57 UTC | START FROM HOME FOR THE FASTEST FLOW</t>
   </si>
   <si>
     <t>Back to HOME</t>
@@ -584,7 +584,7 @@
     <t>Identity, bio headline, social links, and testimonial section copy.</t>
   </si>
   <si>
-    <t>PRIMARY EDIT SURFACE | LAST SYNC 2026-06-21 23:30:24 UTC</t>
+    <t>PRIMARY EDIT SURFACE | LAST SYNC 2026-06-22 17:47:57 UTC</t>
   </si>
   <si>
     <t>Guide</t>
@@ -740,7 +740,7 @@
     <t>CV_PENDING</t>
   </si>
   <si>
-    <t>/manifest-test.pdf</t>
+    <t>/Alberto_Medina_CV_2026.pdf</t>
   </si>
   <si>
     <t>Main project cards, value story, media wiring, and ordering.</t>
@@ -1631,7 +1631,7 @@
     <t>Brand lockup and terminal button label.</t>
   </si>
   <si>
-    <t>ADVANCED DATA SHEET | LAST SYNC 2026-06-21 23:30:24 UTC</t>
+    <t>ADVANCED DATA SHEET | LAST SYNC 2026-06-22 17:47:57 UTC</t>
   </si>
   <si>
     <t>Supporting data sheet. Changes here feed one or more primary editing surfaces.</t>

--- a/src/data/content/portfolio-master.xlsx
+++ b/src/data/content/portfolio-master.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="716">
   <si>
     <t>Portfolio Content Hub</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Edit the workbook from a single control center, then sync the site.</t>
   </si>
   <si>
-    <t>MASTER WORKBOOK | LAST SYNC 2026-06-22 17:47:57 UTC | CTRL+CLICK LINKS TO NAVIGATE</t>
+    <t>MASTER WORKBOOK | LAST SYNC 2026-06-22 20:02:49 UTC | CTRL+CLICK LINKS TO NAVIGATE</t>
   </si>
   <si>
     <t>Use the cards below for primary editing, the workflow panel for the sync cycle, and the grouped panels at the bottom for advanced sheets.</t>
@@ -223,7 +223,7 @@
     <t>Editing rules, shortcuts, and the quickest path to each content area.</t>
   </si>
   <si>
-    <t>GUIDE SHEET | LAST SYNC 2026-06-22 17:47:57 UTC | START FROM HOME FOR THE FASTEST FLOW</t>
+    <t>GUIDE SHEET | LAST SYNC 2026-06-22 20:02:49 UTC | START FROM HOME FOR THE FASTEST FLOW</t>
   </si>
   <si>
     <t>Back to HOME</t>
@@ -584,7 +584,7 @@
     <t>Identity, bio headline, social links, and testimonial section copy.</t>
   </si>
   <si>
-    <t>PRIMARY EDIT SURFACE | LAST SYNC 2026-06-22 17:47:57 UTC</t>
+    <t>PRIMARY EDIT SURFACE | LAST SYNC 2026-06-22 20:02:49 UTC</t>
   </si>
   <si>
     <t>Guide</t>
@@ -1631,7 +1631,7 @@
     <t>Brand lockup and terminal button label.</t>
   </si>
   <si>
-    <t>ADVANCED DATA SHEET | LAST SYNC 2026-06-22 17:47:57 UTC</t>
+    <t>ADVANCED DATA SHEET | LAST SYNC 2026-06-22 20:02:49 UTC</t>
   </si>
   <si>
     <t>Supporting data sheet. Changes here feed one or more primary editing surfaces.</t>
@@ -1805,19 +1805,19 @@
     <t>tooltipUsage</t>
   </si>
   <si>
-    <t>zsh - port-folio</t>
-  </si>
-  <si>
-    <t>Click to access system...</t>
-  </si>
-  <si>
-    <t>Terminal Agent</t>
-  </si>
-  <si>
-    <t>Backed by Groq-hosted Llama 3 with live portfolio context.</t>
-  </si>
-  <si>
-    <t>Try asking "What have you built recently?" or "help me scope a system".</t>
+    <t>portfolio-agent -- evidence-mode</t>
+  </si>
+  <si>
+    <t>Open the portfolio guide...</t>
+  </si>
+  <si>
+    <t>Portfolio Guide</t>
+  </si>
+  <si>
+    <t>Grounded in selected projects, CV routes, and live GitHub context when available.</t>
+  </si>
+  <si>
+    <t>Use /help, paste a role after /fit, or ask to compare two systems.</t>
   </si>
   <si>
     <t>Initial and greeting lines for the terminal experience.</t>
@@ -1829,52 +1829,43 @@
     <t>color</t>
   </si>
   <si>
-    <t>&gt;&gt;&gt; SYSTEM_CHECK: READY</t>
+    <t>&gt;&gt;&gt; PORTFOLIO_AGENT: READY</t>
   </si>
   <si>
     <t>INITIAL / READY</t>
   </si>
   <si>
-    <t>&gt;&gt;&gt; DETECTED_VISITOR: AUTH_PENDING...</t>
-  </si>
-  <si>
-    <t>&gt;&gt;&gt; LIVE_GITHUB_SYNC: ACTIVE</t>
-  </si>
-  <si>
-    <t>&gt;&gt;&gt; HINT: Ask about recent builds, stack decisions, or current GitHub activity.</t>
-  </si>
-  <si>
-    <t>&gt;&gt;&gt; COMMANDS: ['chat', 'explore', 'github']</t>
-  </si>
-  <si>
-    <t>&gt;&gt;&gt; STATUS: WAITING_FOR_INPUT...</t>
-  </si>
-  <si>
-    <t>$ ./init_session.sh --interactive</t>
-  </si>
-  <si>
-    <t>&gt; INITIALIZING GUEST SESSION...</t>
+    <t>&gt;&gt;&gt; CONTEXT: PROJECTS + CV + LIVE_GITHUB</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt; MODES: ASK / COMPARE / RECRUITER_FIT</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt; COMMANDS: /help /fit /projects /cv /github /contact</t>
+  </si>
+  <si>
+    <t>&gt; GUEST_SESSION READY</t>
   </si>
   <si>
     <t>GREETING / READY</t>
   </si>
   <si>
-    <t>&gt; ACCESS GRANTED. AWAITING INPUT...</t>
+    <t>&gt; ASK NATURALLY OR RUN /HELP</t>
   </si>
   <si>
     <t>Tooltip bullets that explain what the terminal can do.</t>
   </si>
   <si>
-    <t>Reads live portfolio content and current GitHub activity.</t>
-  </si>
-  <si>
-    <t>Can navigate the site and move between sections.</t>
-  </si>
-  <si>
-    <t>Answers technical questions about projects, stack, and experience.</t>
-  </si>
-  <si>
-    <t>Can help scope incoming project briefs and technical direction.</t>
+    <t>Maps role requirements to specific project evidence and honest gaps.</t>
+  </si>
+  <si>
+    <t>Compares projects, architecture choices, and engineering trade-offs.</t>
+  </si>
+  <si>
+    <t>Opens the CV, selected systems, GitHub, stack, and contact routes.</t>
+  </si>
+  <si>
+    <t>Uses live GitHub activity when available and falls back to portfolio evidence.</t>
   </si>
   <si>
     <t>Section badge ids and two-line labels across the site.</t>
@@ -7247,7 +7238,7 @@
   <sheetPr>
     <tabColor rgb="FF334155"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" style="53" customWidth="1"/>
@@ -7374,7 +7365,7 @@
         <v>593</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D10" s="71">
         <v>2</v>
@@ -7391,7 +7382,7 @@
         <v>594</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D11" s="67">
         <v>3</v>
@@ -7408,7 +7399,7 @@
         <v>595</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D12" s="71">
         <v>4</v>
@@ -7419,88 +7410,58 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="67" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B13" s="68" t="s">
         <v>596</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="D13" s="67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="71" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C14" s="71" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="68" t="s">
-        <v>598</v>
-      </c>
-      <c r="C15" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="67">
-        <v>7</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>592</v>
-      </c>
+      <c r="A15" s="67"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="73"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>599</v>
-      </c>
-      <c r="C16" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="71">
-        <v>1</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>600</v>
-      </c>
+      <c r="A16" s="71"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="73"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="68" t="s">
-        <v>601</v>
-      </c>
-      <c r="C17" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="67">
-        <v>2</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>600</v>
-      </c>
+      <c r="A17" s="67"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="73"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="71"/>
@@ -7552,25 +7513,25 @@
       <c r="E24" s="73"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="67"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="73"/>
+      <c r="A25" s="59"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="71"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="73"/>
+      <c r="A26" s="59"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="67"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="73"/>
+      <c r="A27" s="59"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="59"/>
@@ -7585,27 +7546,6 @@
       <c r="C29" s="59"/>
       <c r="D29" s="59"/>
       <c r="E29" s="59"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:E8"/>
@@ -7617,22 +7557,22 @@
     <mergeCell ref="A7:E7"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="A10:A27">
+    <dataValidation type="list" allowBlank="1" sqref="A10:A24">
       <formula1>'_LOOKUPS'!$H$2:$H$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="A9:A27">
+    <dataValidation type="list" allowBlank="1" sqref="A9:A24">
       <formula1>'_LOOKUPS'!$H$2:$H$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C10:C27">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C24">
       <formula1>'_LOOKUPS'!$G$2:$G$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C9:C27">
+    <dataValidation type="list" allowBlank="1" sqref="C9:C24">
       <formula1>'_LOOKUPS'!$G$2:$G$5</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" sqref="D10:D27">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" sqref="D10:D24">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" sqref="D9:D27">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" sqref="D9:D24">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -7669,7 +7609,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -7730,7 +7670,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B9" s="67">
         <v>1</v>
@@ -7741,7 +7681,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="72" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B10" s="71">
         <v>2</v>
@@ -7752,7 +7692,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B11" s="67">
         <v>3</v>
@@ -7763,7 +7703,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B12" s="71">
         <v>4</v>
@@ -7890,7 +7830,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -7960,16 +7900,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>233</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E8" s="65" t="s">
         <v>245</v>
@@ -7983,13 +7923,13 @@
         <v>111</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E9" s="67">
         <v>1</v>
@@ -8003,13 +7943,13 @@
         <v>123</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E10" s="71">
         <v>2</v>
@@ -8023,13 +7963,13 @@
         <v>132</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D11" s="67" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E11" s="67">
         <v>3</v>
@@ -8043,13 +7983,13 @@
         <v>140</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E12" s="71">
         <v>4</v>
@@ -8063,13 +8003,13 @@
         <v>143</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E13" s="67">
         <v>5</v>
@@ -8805,7 +8745,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -8875,7 +8815,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>234</v>
@@ -8898,7 +8838,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C9" s="67" t="s">
         <v>106</v>
@@ -8918,7 +8858,7 @@
         <v>122</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C10" s="71" t="s">
         <v>118</v>
@@ -8938,7 +8878,7 @@
         <v>131</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>128</v>
@@ -8958,7 +8898,7 @@
         <v>139</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>136</v>
@@ -9124,7 +9064,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -9182,7 +9122,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>371</v>
@@ -9199,7 +9139,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -9213,7 +9153,7 @@
         <v>110</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -9227,7 +9167,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C11" s="67">
         <v>3</v>
@@ -9241,7 +9181,7 @@
         <v>110</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C12" s="71">
         <v>4</v>
@@ -9255,7 +9195,7 @@
         <v>110</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C13" s="67">
         <v>5</v>
@@ -9269,7 +9209,7 @@
         <v>110</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C14" s="71">
         <v>6</v>
@@ -9283,7 +9223,7 @@
         <v>122</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C15" s="67">
         <v>1</v>
@@ -9297,7 +9237,7 @@
         <v>122</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C16" s="71">
         <v>2</v>
@@ -9311,7 +9251,7 @@
         <v>122</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C17" s="67">
         <v>3</v>
@@ -9325,7 +9265,7 @@
         <v>122</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C18" s="71">
         <v>4</v>
@@ -9339,7 +9279,7 @@
         <v>122</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C19" s="67">
         <v>5</v>
@@ -9353,7 +9293,7 @@
         <v>131</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C20" s="71">
         <v>1</v>
@@ -9367,7 +9307,7 @@
         <v>131</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C21" s="67">
         <v>2</v>
@@ -9381,7 +9321,7 @@
         <v>131</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C22" s="71">
         <v>3</v>
@@ -9395,7 +9335,7 @@
         <v>131</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C23" s="67">
         <v>4</v>
@@ -9409,7 +9349,7 @@
         <v>131</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C24" s="71">
         <v>5</v>
@@ -9423,7 +9363,7 @@
         <v>139</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C25" s="67">
         <v>1</v>
@@ -9437,7 +9377,7 @@
         <v>139</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C26" s="71">
         <v>2</v>
@@ -9451,7 +9391,7 @@
         <v>139</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C27" s="67">
         <v>3</v>
@@ -9465,7 +9405,7 @@
         <v>139</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C28" s="71">
         <v>4</v>
@@ -9479,7 +9419,7 @@
         <v>139</v>
       </c>
       <c r="B29" s="67" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C29" s="67">
         <v>5</v>
@@ -9493,7 +9433,7 @@
         <v>139</v>
       </c>
       <c r="B30" s="71" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C30" s="71">
         <v>6</v>
@@ -9661,7 +9601,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -9721,7 +9661,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>371</v>
@@ -9738,7 +9678,7 @@
         <v>99</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -9752,7 +9692,7 @@
         <v>99</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -9766,7 +9706,7 @@
         <v>99</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C11" s="67">
         <v>3</v>
@@ -9780,7 +9720,7 @@
         <v>99</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C12" s="71">
         <v>4</v>
@@ -9794,7 +9734,7 @@
         <v>113</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C13" s="67">
         <v>1</v>
@@ -9808,7 +9748,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C14" s="71">
         <v>2</v>
@@ -9822,7 +9762,7 @@
         <v>113</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C15" s="67">
         <v>3</v>
@@ -9836,7 +9776,7 @@
         <v>113</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C16" s="71">
         <v>4</v>
@@ -9850,7 +9790,7 @@
         <v>124</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C17" s="67">
         <v>1</v>
@@ -9864,7 +9804,7 @@
         <v>124</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C18" s="71">
         <v>2</v>
@@ -9878,7 +9818,7 @@
         <v>124</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C19" s="67">
         <v>3</v>
@@ -9892,7 +9832,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C20" s="71">
         <v>4</v>
@@ -9906,7 +9846,7 @@
         <v>133</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C21" s="67">
         <v>1</v>
@@ -9920,7 +9860,7 @@
         <v>133</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C22" s="71">
         <v>2</v>
@@ -9934,7 +9874,7 @@
         <v>133</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C23" s="67">
         <v>3</v>
@@ -9948,7 +9888,7 @@
         <v>133</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C24" s="71">
         <v>4</v>
@@ -9962,7 +9902,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C25" s="67">
         <v>1</v>
@@ -9976,7 +9916,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C26" s="71">
         <v>2</v>
@@ -9990,7 +9930,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C27" s="67">
         <v>3</v>
@@ -10004,7 +9944,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C28" s="71">
         <v>4</v>
@@ -10181,7 +10121,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -10241,7 +10181,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B8" s="65" t="s">
         <v>371</v>
@@ -10258,7 +10198,7 @@
         <v>99</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C9" s="67">
         <v>1</v>
@@ -10272,7 +10212,7 @@
         <v>99</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C10" s="71">
         <v>2</v>
@@ -10286,7 +10226,7 @@
         <v>99</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C11" s="67">
         <v>3</v>
@@ -10300,7 +10240,7 @@
         <v>99</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C12" s="71">
         <v>4</v>
@@ -10314,7 +10254,7 @@
         <v>113</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C13" s="67">
         <v>1</v>
@@ -10328,7 +10268,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C14" s="71">
         <v>2</v>
@@ -10342,7 +10282,7 @@
         <v>113</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C15" s="67">
         <v>3</v>
@@ -10356,7 +10296,7 @@
         <v>113</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C16" s="71">
         <v>4</v>
@@ -10370,7 +10310,7 @@
         <v>124</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C17" s="67">
         <v>1</v>
@@ -10384,7 +10324,7 @@
         <v>124</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C18" s="71">
         <v>2</v>
@@ -10398,7 +10338,7 @@
         <v>124</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C19" s="67">
         <v>3</v>
@@ -10412,7 +10352,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C20" s="71">
         <v>4</v>
@@ -10426,7 +10366,7 @@
         <v>133</v>
       </c>
       <c r="B21" s="67" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C21" s="67">
         <v>1</v>
@@ -10440,7 +10380,7 @@
         <v>133</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C22" s="71">
         <v>2</v>
@@ -10454,7 +10394,7 @@
         <v>133</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C23" s="67">
         <v>3</v>
@@ -10468,7 +10408,7 @@
         <v>133</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C24" s="71">
         <v>4</v>
@@ -10482,7 +10422,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C25" s="67">
         <v>1</v>
@@ -10496,7 +10436,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C26" s="71">
         <v>2</v>
@@ -10510,7 +10450,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C27" s="67">
         <v>3</v>
@@ -10524,7 +10464,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C28" s="71">
         <v>4</v>
@@ -10706,7 +10646,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -10785,7 +10725,7 @@
         <v>276</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>371</v>
@@ -10794,7 +10734,7 @@
         <v>278</v>
       </c>
       <c r="E8" s="65" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F8" s="65" t="s">
         <v>245</v>
@@ -10808,16 +10748,16 @@
         <v>108</v>
       </c>
       <c r="B9" s="67" t="s">
+        <v>686</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>687</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>688</v>
+      </c>
+      <c r="E9" s="67" t="s">
         <v>689</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>690</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>691</v>
-      </c>
-      <c r="E9" s="67" t="s">
-        <v>692</v>
       </c>
       <c r="F9" s="67">
         <v>1</v>
@@ -10831,16 +10771,16 @@
         <v>120</v>
       </c>
       <c r="B10" s="71" t="s">
+        <v>690</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>691</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>692</v>
+      </c>
+      <c r="E10" s="71" t="s">
         <v>693</v>
-      </c>
-      <c r="C10" s="71" t="s">
-        <v>694</v>
-      </c>
-      <c r="D10" s="71" t="s">
-        <v>695</v>
-      </c>
-      <c r="E10" s="71" t="s">
-        <v>696</v>
       </c>
       <c r="F10" s="71">
         <v>2</v>
@@ -11003,7 +10943,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -11078,7 +11018,7 @@
         <v>185</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>125</v>
@@ -11095,7 +11035,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B9" s="67" t="s">
         <v>203</v>
@@ -11115,7 +11055,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B10" s="71" t="s">
         <v>204</v>
@@ -11135,10 +11075,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>129</v>
@@ -11158,7 +11098,7 @@
         <v>137</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>137</v>
@@ -11326,7 +11266,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -11400,7 +11340,7 @@
         <v>560</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>245</v>
@@ -11411,13 +11351,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D9" s="67">
         <v>1</v>
@@ -11428,10 +11368,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C10" s="71" t="s">
         <v>252</v>
@@ -11445,10 +11385,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>252</v>
@@ -11591,7 +11531,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -11658,13 +11598,13 @@
         <v>185</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E8" s="66" t="s">
         <v>196</v>
@@ -11675,13 +11615,13 @@
         <v>197</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C9" s="67" t="s">
         <v>576</v>
       </c>
       <c r="D9" s="67" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E9" s="70" t="s">
         <v>207</v>
